--- a/CTR_Sample_Template.xlsx
+++ b/CTR_Sample_Template.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="795" uniqueCount="218">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="796" uniqueCount="219">
   <si>
     <t>id</t>
   </si>
@@ -675,6 +675,9 @@
   </si>
   <si>
     <t>date</t>
+  </si>
+  <si>
+    <t>madeby</t>
   </si>
 </sst>
 </file>
@@ -691,7 +694,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFA5D6FF"/>
+      <color theme="1"/>
       <name val="Consolas"/>
       <family val="3"/>
     </font>
@@ -1015,7 +1018,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:M2"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="4" style="1" customWidth="1"/>
@@ -1029,7 +1032,7 @@
     <col min="9" max="9" width="14" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:13">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1066,8 +1069,11 @@
       <c r="L1" s="1" t="s">
         <v>217</v>
       </c>
-    </row>
-    <row r="2" spans="1:12">
+      <c r="M1" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
       <c r="A2" s="1">
         <v>1</v>
       </c>

--- a/CTR_Sample_Template.xlsx
+++ b/CTR_Sample_Template.xlsx
@@ -21,14 +21,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="796" uniqueCount="219">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="795" uniqueCount="218">
   <si>
     <t>id</t>
   </si>
   <si>
-    <t>name</t>
-  </si>
-  <si>
     <t>station_name</t>
   </si>
   <si>
@@ -665,19 +662,19 @@
     <t xml:space="preserve">EWUYN KEY </t>
   </si>
   <si>
-    <t>sig_play_no</t>
-  </si>
-  <si>
-    <t>ver_no</t>
-  </si>
-  <si>
     <t>page_no</t>
   </si>
   <si>
     <t>date</t>
   </si>
   <si>
-    <t>madeby</t>
+    <t>total_page_no</t>
+  </si>
+  <si>
+    <t>sip_no</t>
+  </si>
+  <si>
+    <t>ctr_name</t>
   </si>
 </sst>
 </file>
@@ -1018,11 +1015,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M2"/>
+  <dimension ref="A1:L2"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="4" style="1" customWidth="1"/>
-    <col min="2" max="2" width="7" style="1" customWidth="1"/>
+    <col min="2" max="2" width="12.140625" style="1" customWidth="1"/>
     <col min="3" max="3" width="17" style="1" customWidth="1"/>
     <col min="4" max="4" width="12" style="1" customWidth="1"/>
     <col min="5" max="5" width="24" style="1" customWidth="1"/>
@@ -1030,58 +1027,56 @@
     <col min="7" max="7" width="11" style="1" customWidth="1"/>
     <col min="8" max="8" width="9" style="1" customWidth="1"/>
     <col min="9" max="9" width="14" style="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1</v>
+        <v>217</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
       <c r="I1" s="3" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>215</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="M1" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12">
       <c r="A2" s="1">
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>8</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>9</v>
       </c>
       <c r="D2" s="1">
         <v>8</v>
@@ -1090,16 +1085,16 @@
         <v>72</v>
       </c>
       <c r="F2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="H2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="I2" s="1" t="s">
         <v>12</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -1119,19 +1114,19 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>17</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -1139,13 +1134,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="D2" s="1" t="s">
         <v>20</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -1153,13 +1148,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="D3" s="1" t="s">
         <v>23</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -1167,13 +1162,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -1181,13 +1176,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -1195,13 +1190,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -1209,13 +1204,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -1223,13 +1218,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C8" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="D8" s="1" t="s">
         <v>30</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -1237,13 +1232,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C9" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="D9" s="1" t="s">
         <v>33</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -1251,13 +1246,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -1265,13 +1260,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -1297,68 +1292,68 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>41</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B2" s="1">
+        <v>2</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="B2" s="1">
-        <v>2</v>
-      </c>
-      <c r="C2" s="1" t="s">
+      <c r="D2" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="E2" s="1">
+        <v>1</v>
+      </c>
+      <c r="F2" s="1">
+        <v>2</v>
+      </c>
+      <c r="G2" s="1">
+        <v>2</v>
+      </c>
+      <c r="H2" s="2" t="s">
         <v>45</v>
-      </c>
-      <c r="E2" s="1">
-        <v>1</v>
-      </c>
-      <c r="F2" s="1">
-        <v>2</v>
-      </c>
-      <c r="G2" s="1">
-        <v>2</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B3" s="1">
         <v>2</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E3" s="1">
         <v>3</v>
@@ -1370,21 +1365,21 @@
         <v>2</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B4" s="1">
         <v>2</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E4" s="1">
         <v>5</v>
@@ -1396,21 +1391,21 @@
         <v>2</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B5" s="1">
         <v>2</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E5" s="1">
         <v>7</v>
@@ -1422,21 +1417,21 @@
         <v>2</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B6" s="1">
         <v>4</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E6" s="1">
         <v>9</v>
@@ -1448,21 +1443,21 @@
         <v>2</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B7" s="1">
         <v>12</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E7" s="1">
         <v>13</v>
@@ -1474,47 +1469,47 @@
         <v>2</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B8" s="1">
         <v>2</v>
       </c>
       <c r="C8" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D8" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D8" s="1" t="s">
+      <c r="E8" s="1">
+        <v>1</v>
+      </c>
+      <c r="F8" s="1">
+        <v>2</v>
+      </c>
+      <c r="G8" s="1">
+        <v>2</v>
+      </c>
+      <c r="H8" s="2" t="s">
         <v>56</v>
-      </c>
-      <c r="E8" s="1">
-        <v>1</v>
-      </c>
-      <c r="F8" s="1">
-        <v>2</v>
-      </c>
-      <c r="G8" s="1">
-        <v>2</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B9" s="1">
         <v>2</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E9" s="1">
         <v>3</v>
@@ -1526,21 +1521,21 @@
         <v>2</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="10" spans="1:8">
       <c r="A10" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B10" s="1">
         <v>2</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E10" s="1">
         <v>5</v>
@@ -1552,21 +1547,21 @@
         <v>2</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="11" spans="1:8">
       <c r="A11" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B11" s="1">
         <v>2</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E11" s="1">
         <v>7</v>
@@ -1578,21 +1573,21 @@
         <v>2</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="12" spans="1:8">
       <c r="A12" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B12" s="1">
         <v>4</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E12" s="1">
         <v>9</v>
@@ -1604,21 +1599,21 @@
         <v>2</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="13" spans="1:8">
       <c r="A13" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B13" s="1">
         <v>12</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E13" s="1">
         <v>13</v>
@@ -1630,22 +1625,22 @@
         <v>2</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="14" spans="1:8">
       <c r="A14" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B14" s="1">
         <v>2</v>
       </c>
       <c r="C14" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="D14" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="D14" s="1" t="s">
-        <v>63</v>
-      </c>
       <c r="E14" s="1">
         <v>1</v>
       </c>
@@ -1656,21 +1651,21 @@
         <v>2</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="15" spans="1:8">
       <c r="A15" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B15" s="1">
         <v>2</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E15" s="1">
         <v>3</v>
@@ -1682,21 +1677,21 @@
         <v>2</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="16" spans="1:8">
       <c r="A16" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B16" s="1">
         <v>2</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E16" s="1">
         <v>5</v>
@@ -1708,21 +1703,21 @@
         <v>2</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="17" spans="1:8">
       <c r="A17" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B17" s="1">
         <v>2</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E17" s="1">
         <v>7</v>
@@ -1734,21 +1729,21 @@
         <v>2</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18" spans="1:8">
       <c r="A18" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B18" s="1">
         <v>2</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E18" s="1">
         <v>9</v>
@@ -1760,21 +1755,21 @@
         <v>2</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="19" spans="1:8">
       <c r="A19" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B19" s="1">
         <v>2</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E19" s="1">
         <v>11</v>
@@ -1786,21 +1781,21 @@
         <v>2</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="20" spans="1:8">
       <c r="A20" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B20" s="1">
         <v>2</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E20" s="1">
         <v>13</v>
@@ -1812,21 +1807,21 @@
         <v>2</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="21" spans="1:8">
       <c r="A21" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B21" s="1">
         <v>2</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E21" s="1">
         <v>15</v>
@@ -1838,21 +1833,21 @@
         <v>2</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="22" spans="1:8">
       <c r="A22" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B22" s="1">
         <v>2</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E22" s="1">
         <v>17</v>
@@ -1864,21 +1859,21 @@
         <v>2</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="23" spans="1:8">
       <c r="A23" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B23" s="1">
         <v>2</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E23" s="1">
         <v>19</v>
@@ -1890,21 +1885,21 @@
         <v>2</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="24" spans="1:8">
       <c r="A24" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B24" s="1">
         <v>2</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E24" s="1">
         <v>21</v>
@@ -1916,21 +1911,21 @@
         <v>2</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="25" spans="1:8">
       <c r="A25" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B25" s="1">
         <v>2</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E25" s="1">
         <v>23</v>
@@ -1942,22 +1937,22 @@
         <v>2</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="26" spans="1:8">
       <c r="A26" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B26" s="1">
         <v>2</v>
       </c>
       <c r="C26" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="D26" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="D26" s="1" t="s">
-        <v>71</v>
-      </c>
       <c r="E26" s="1">
         <v>1</v>
       </c>
@@ -1968,21 +1963,21 @@
         <v>2</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="27" spans="1:8">
       <c r="A27" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B27" s="1">
         <v>2</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E27" s="1">
         <v>3</v>
@@ -1994,21 +1989,21 @@
         <v>2</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="28" spans="1:8">
       <c r="A28" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B28" s="1">
         <v>2</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E28" s="1">
         <v>5</v>
@@ -2020,21 +2015,21 @@
         <v>2</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="29" spans="1:8">
       <c r="A29" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B29" s="1">
         <v>2</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E29" s="1">
         <v>7</v>
@@ -2046,21 +2041,21 @@
         <v>2</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="30" spans="1:8">
       <c r="A30" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B30" s="1">
         <v>2</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E30" s="1">
         <v>9</v>
@@ -2072,21 +2067,21 @@
         <v>2</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="31" spans="1:8">
       <c r="A31" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B31" s="1">
         <v>2</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E31" s="1">
         <v>11</v>
@@ -2098,21 +2093,21 @@
         <v>2</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="32" spans="1:8">
       <c r="A32" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B32" s="1">
         <v>2</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E32" s="1">
         <v>13</v>
@@ -2124,21 +2119,21 @@
         <v>2</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="33" spans="1:8">
       <c r="A33" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B33" s="1">
         <v>2</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E33" s="1">
         <v>15</v>
@@ -2150,21 +2145,21 @@
         <v>2</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="34" spans="1:8">
       <c r="A34" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B34" s="1">
         <v>2</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E34" s="1">
         <v>17</v>
@@ -2176,21 +2171,21 @@
         <v>2</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="35" spans="1:8">
       <c r="A35" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B35" s="1">
         <v>2</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E35" s="1">
         <v>19</v>
@@ -2202,21 +2197,21 @@
         <v>2</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="36" spans="1:8">
       <c r="A36" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B36" s="1">
         <v>2</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E36" s="1">
         <v>21</v>
@@ -2228,21 +2223,21 @@
         <v>2</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="37" spans="1:8">
       <c r="A37" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B37" s="1">
         <v>2</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E37" s="1">
         <v>23</v>
@@ -2254,22 +2249,22 @@
         <v>2</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="38" spans="1:8">
       <c r="A38" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B38" s="1">
         <v>2</v>
       </c>
       <c r="C38" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="D38" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D38" s="1" t="s">
-        <v>79</v>
-      </c>
       <c r="E38" s="1">
         <v>1</v>
       </c>
@@ -2280,21 +2275,21 @@
         <v>2</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="39" spans="1:8">
       <c r="A39" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B39" s="1">
         <v>10</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E39" s="1">
         <v>3</v>
@@ -2306,21 +2301,21 @@
         <v>2</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="40" spans="1:8">
       <c r="A40" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B40" s="1">
         <v>10</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E40" s="1">
         <v>13</v>
@@ -2332,21 +2327,21 @@
         <v>2</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="41" spans="1:8">
       <c r="A41" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B41" s="1">
         <v>2</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E41" s="1">
         <v>23</v>
@@ -2358,22 +2353,22 @@
         <v>2</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="42" spans="1:8">
       <c r="A42" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B42" s="1">
         <v>2</v>
       </c>
       <c r="C42" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="D42" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="D42" s="1" t="s">
-        <v>82</v>
-      </c>
       <c r="E42" s="1">
         <v>1</v>
       </c>
@@ -2384,21 +2379,21 @@
         <v>2</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="43" spans="1:8">
       <c r="A43" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B43" s="1">
         <v>2</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E43" s="1">
         <v>3</v>
@@ -2410,21 +2405,21 @@
         <v>2</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="44" spans="1:8">
       <c r="A44" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B44" s="1">
         <v>2</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E44" s="1">
         <v>5</v>
@@ -2436,21 +2431,21 @@
         <v>2</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="45" spans="1:8">
       <c r="A45" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B45" s="1">
         <v>2</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E45" s="1">
         <v>7</v>
@@ -2462,21 +2457,21 @@
         <v>2</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="46" spans="1:8">
       <c r="A46" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B46" s="1">
         <v>2</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E46" s="1">
         <v>9</v>
@@ -2488,21 +2483,21 @@
         <v>2</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="47" spans="1:8">
       <c r="A47" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B47" s="1">
         <v>2</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E47" s="1">
         <v>11</v>
@@ -2514,21 +2509,21 @@
         <v>2</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="48" spans="1:8">
       <c r="A48" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B48" s="1">
         <v>2</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E48" s="1">
         <v>13</v>
@@ -2540,21 +2535,21 @@
         <v>2</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="49" spans="1:8">
       <c r="A49" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B49" s="1">
         <v>10</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E49" s="1">
         <v>15</v>
@@ -2566,21 +2561,21 @@
         <v>2</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="50" spans="1:8">
       <c r="A50" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B50" s="1">
         <v>24</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E50" s="1">
         <v>1</v>
@@ -2592,22 +2587,22 @@
         <v>2</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="51" spans="1:8">
       <c r="A51" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B51" s="1">
         <v>2</v>
       </c>
       <c r="C51" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="D51" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="D51" s="1" t="s">
-        <v>92</v>
-      </c>
       <c r="E51" s="1">
         <v>1</v>
       </c>
@@ -2618,21 +2613,21 @@
         <v>2</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="52" spans="1:8">
       <c r="A52" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B52" s="1">
         <v>2</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E52" s="1">
         <v>3</v>
@@ -2644,21 +2639,21 @@
         <v>2</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="53" spans="1:8">
       <c r="A53" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B53" s="1">
         <v>2</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E53" s="1">
         <v>5</v>
@@ -2670,21 +2665,21 @@
         <v>2</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="54" spans="1:8">
       <c r="A54" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B54" s="1">
         <v>6</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E54" s="1">
         <v>1</v>
@@ -2696,22 +2691,22 @@
         <v>2</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="55" spans="1:8">
       <c r="A55" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B55" s="1">
         <v>2</v>
       </c>
       <c r="C55" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="D55" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="D55" s="1" t="s">
-        <v>97</v>
-      </c>
       <c r="E55" s="1">
         <v>1</v>
       </c>
@@ -2722,21 +2717,21 @@
         <v>2</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="56" spans="1:8">
       <c r="A56" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B56" s="1">
         <v>2</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E56" s="1">
         <v>3</v>
@@ -2748,21 +2743,21 @@
         <v>2</v>
       </c>
       <c r="H56" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="57" spans="1:8">
       <c r="A57" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B57" s="1">
         <v>2</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E57" s="1">
         <v>5</v>
@@ -2774,22 +2769,22 @@
         <v>2</v>
       </c>
       <c r="H57" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="58" spans="1:8">
       <c r="A58" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B58" s="1">
         <v>2</v>
       </c>
       <c r="C58" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="D58" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="D58" s="1" t="s">
-        <v>100</v>
-      </c>
       <c r="E58" s="1">
         <v>1</v>
       </c>
@@ -2800,21 +2795,21 @@
         <v>2</v>
       </c>
       <c r="H58" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="59" spans="1:8">
       <c r="A59" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B59" s="1">
         <v>4</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E59" s="1">
         <v>3</v>
@@ -2826,21 +2821,21 @@
         <v>2</v>
       </c>
       <c r="H59" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="60" spans="1:8">
       <c r="A60" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B60" s="1">
         <v>6</v>
       </c>
       <c r="C60" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="D60" s="1" t="s">
         <v>101</v>
-      </c>
-      <c r="D60" s="1" t="s">
-        <v>102</v>
       </c>
       <c r="E60" s="1">
         <v>1</v>
@@ -2852,21 +2847,21 @@
         <v>2</v>
       </c>
       <c r="H60" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="61" spans="1:8">
       <c r="A61" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B61" s="1">
         <v>6</v>
       </c>
       <c r="C61" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="D61" s="1" t="s">
         <v>103</v>
-      </c>
-      <c r="D61" s="1" t="s">
-        <v>104</v>
       </c>
       <c r="E61" s="1">
         <v>1</v>
@@ -2878,21 +2873,21 @@
         <v>2</v>
       </c>
       <c r="H61" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="62" spans="1:8">
       <c r="A62" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B62" s="1">
         <v>6</v>
       </c>
       <c r="C62" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="D62" s="1" t="s">
         <v>105</v>
-      </c>
-      <c r="D62" s="1" t="s">
-        <v>106</v>
       </c>
       <c r="E62" s="1">
         <v>1</v>
@@ -2904,21 +2899,21 @@
         <v>2</v>
       </c>
       <c r="H62" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="63" spans="1:8">
       <c r="A63" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B63" s="1">
         <v>6</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E63" s="1">
         <v>1</v>
@@ -2930,22 +2925,22 @@
         <v>2</v>
       </c>
       <c r="H63" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="64" spans="1:8">
       <c r="A64" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="B64" s="1">
+        <v>2</v>
+      </c>
+      <c r="C64" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="B64" s="1">
-        <v>2</v>
-      </c>
-      <c r="C64" s="1" t="s">
+      <c r="D64" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="D64" s="1" t="s">
-        <v>110</v>
-      </c>
       <c r="E64" s="1">
         <v>1</v>
       </c>
@@ -2956,21 +2951,21 @@
         <v>2</v>
       </c>
       <c r="H64" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="65" spans="1:8">
       <c r="A65" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B65" s="1">
         <v>2</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E65" s="1">
         <v>3</v>
@@ -2982,21 +2977,21 @@
         <v>2</v>
       </c>
       <c r="H65" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="66" spans="1:8">
       <c r="A66" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B66" s="1">
         <v>2</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E66" s="1">
         <v>5</v>
@@ -3008,21 +3003,21 @@
         <v>2</v>
       </c>
       <c r="H66" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="67" spans="1:8">
       <c r="A67" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B67" s="1">
         <v>6</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E67" s="1">
         <v>7</v>
@@ -3034,21 +3029,21 @@
         <v>2</v>
       </c>
       <c r="H67" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="68" spans="1:8">
       <c r="A68" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B68" s="1">
         <v>2</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E68" s="1">
         <v>13</v>
@@ -3060,21 +3055,21 @@
         <v>2</v>
       </c>
       <c r="H68" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="69" spans="1:8">
       <c r="A69" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B69" s="1">
         <v>2</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E69" s="1">
         <v>15</v>
@@ -3086,21 +3081,21 @@
         <v>2</v>
       </c>
       <c r="H69" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="70" spans="1:8">
       <c r="A70" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B70" s="1">
         <v>2</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E70" s="1">
         <v>17</v>
@@ -3112,21 +3107,21 @@
         <v>2</v>
       </c>
       <c r="H70" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="71" spans="1:8">
       <c r="A71" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B71" s="1">
         <v>2</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E71" s="1">
         <v>19</v>
@@ -3138,21 +3133,21 @@
         <v>2</v>
       </c>
       <c r="H71" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="72" spans="1:8">
       <c r="A72" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B72" s="1">
         <v>4</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E72" s="1">
         <v>21</v>
@@ -3164,22 +3159,22 @@
         <v>2</v>
       </c>
       <c r="H72" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="73" spans="1:8">
       <c r="A73" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B73" s="1">
         <v>2</v>
       </c>
       <c r="C73" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="D73" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="D73" s="1" t="s">
-        <v>118</v>
-      </c>
       <c r="E73" s="1">
         <v>1</v>
       </c>
@@ -3190,21 +3185,21 @@
         <v>2</v>
       </c>
       <c r="H73" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="74" spans="1:8">
       <c r="A74" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B74" s="1">
         <v>2</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E74" s="1">
         <v>3</v>
@@ -3216,21 +3211,21 @@
         <v>2</v>
       </c>
       <c r="H74" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="75" spans="1:8">
       <c r="A75" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B75" s="1">
         <v>2</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E75" s="1">
         <v>5</v>
@@ -3242,21 +3237,21 @@
         <v>2</v>
       </c>
       <c r="H75" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="76" spans="1:8">
       <c r="A76" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B76" s="1">
         <v>6</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E76" s="1">
         <v>7</v>
@@ -3268,21 +3263,21 @@
         <v>2</v>
       </c>
       <c r="H76" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="77" spans="1:8">
       <c r="A77" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B77" s="1">
         <v>12</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E77" s="1">
         <v>13</v>
@@ -3294,21 +3289,21 @@
         <v>2</v>
       </c>
       <c r="H77" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="78" spans="1:8">
       <c r="A78" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B78" s="1">
         <v>6</v>
       </c>
       <c r="C78" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="D78" s="1" t="s">
         <v>121</v>
-      </c>
-      <c r="D78" s="1" t="s">
-        <v>122</v>
       </c>
       <c r="E78" s="1">
         <v>1</v>
@@ -3320,21 +3315,21 @@
         <v>2</v>
       </c>
       <c r="H78" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="79" spans="1:8">
       <c r="A79" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B79" s="1">
         <v>6</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E79" s="1">
         <v>7</v>
@@ -3346,21 +3341,21 @@
         <v>2</v>
       </c>
       <c r="H79" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="80" spans="1:8">
       <c r="A80" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B80" s="1">
         <v>6</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E80" s="1">
         <v>13</v>
@@ -3372,21 +3367,21 @@
         <v>2</v>
       </c>
       <c r="H80" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="81" spans="1:8">
       <c r="A81" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B81" s="1">
         <v>6</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E81" s="1">
         <v>19</v>
@@ -3398,21 +3393,21 @@
         <v>2</v>
       </c>
       <c r="H81" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="82" spans="1:8">
       <c r="A82" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B82" s="1">
         <v>6</v>
       </c>
       <c r="C82" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="D82" s="1" t="s">
         <v>126</v>
-      </c>
-      <c r="D82" s="1" t="s">
-        <v>127</v>
       </c>
       <c r="E82" s="1">
         <v>1</v>
@@ -3424,21 +3419,21 @@
         <v>2</v>
       </c>
       <c r="H82" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="83" spans="1:8">
       <c r="A83" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B83" s="1">
         <v>6</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E83" s="1">
         <v>7</v>
@@ -3450,21 +3445,21 @@
         <v>2</v>
       </c>
       <c r="H83" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="84" spans="1:8">
       <c r="A84" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B84" s="1">
         <v>6</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E84" s="1">
         <v>13</v>
@@ -3476,21 +3471,21 @@
         <v>2</v>
       </c>
       <c r="H84" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="85" spans="1:8">
       <c r="A85" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B85" s="1">
         <v>6</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E85" s="1">
         <v>19</v>
@@ -3502,21 +3497,21 @@
         <v>2</v>
       </c>
       <c r="H85" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="86" spans="1:8">
       <c r="A86" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B86" s="1">
         <v>4</v>
       </c>
       <c r="C86" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="D86" s="1" t="s">
         <v>130</v>
-      </c>
-      <c r="D86" s="1" t="s">
-        <v>131</v>
       </c>
       <c r="E86" s="1">
         <v>1</v>
@@ -3528,21 +3523,21 @@
         <v>2</v>
       </c>
       <c r="H86" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="87" spans="1:8">
       <c r="A87" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B87" s="1">
         <v>2</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E87" s="1">
         <v>5</v>
@@ -3554,12 +3549,12 @@
         <v>2</v>
       </c>
       <c r="H87" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="88" spans="1:8">
       <c r="A88" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B88" s="1">
         <v>6</v>
@@ -3568,22 +3563,22 @@
         <v>2</v>
       </c>
       <c r="H88" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="89" spans="1:8">
       <c r="A89" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B89" s="1">
         <v>2</v>
       </c>
       <c r="C89" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="D89" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="D89" s="1" t="s">
-        <v>133</v>
-      </c>
       <c r="E89" s="1">
         <v>1</v>
       </c>
@@ -3594,21 +3589,21 @@
         <v>2</v>
       </c>
       <c r="H89" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="90" spans="1:8">
       <c r="A90" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B90" s="1">
         <v>2</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E90" s="1">
         <v>3</v>
@@ -3620,21 +3615,21 @@
         <v>2</v>
       </c>
       <c r="H90" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="91" spans="1:8">
       <c r="A91" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B91" s="1">
         <v>2</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E91" s="1">
         <v>5</v>
@@ -3646,21 +3641,21 @@
         <v>2</v>
       </c>
       <c r="H91" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="92" spans="1:8">
       <c r="A92" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B92" s="1">
         <v>2</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E92" s="1">
         <v>7</v>
@@ -3672,21 +3667,21 @@
         <v>2</v>
       </c>
       <c r="H92" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="93" spans="1:8">
       <c r="A93" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B93" s="1">
         <v>4</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E93" s="1">
         <v>9</v>
@@ -3698,21 +3693,21 @@
         <v>2</v>
       </c>
       <c r="H93" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="94" spans="1:8">
       <c r="A94" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B94" s="1">
         <v>2</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E94" s="1">
         <v>13</v>
@@ -3724,21 +3719,21 @@
         <v>2</v>
       </c>
       <c r="H94" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="95" spans="1:8">
       <c r="A95" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B95" s="1">
         <v>2</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E95" s="1">
         <v>17</v>
@@ -3750,21 +3745,21 @@
         <v>2</v>
       </c>
       <c r="H95" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="96" spans="1:8">
       <c r="A96" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B96" s="1">
         <v>2</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E96" s="1">
         <v>19</v>
@@ -3776,21 +3771,21 @@
         <v>2</v>
       </c>
       <c r="H96" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="97" spans="1:8">
       <c r="A97" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B97" s="1">
         <v>6</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E97" s="1">
         <v>21</v>
@@ -3802,22 +3797,22 @@
         <v>2</v>
       </c>
       <c r="H97" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="98" spans="1:8">
       <c r="A98" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B98" s="1">
         <v>2</v>
       </c>
       <c r="C98" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="D98" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="D98" s="1" t="s">
-        <v>141</v>
-      </c>
       <c r="E98" s="1">
         <v>1</v>
       </c>
@@ -3828,21 +3823,21 @@
         <v>2</v>
       </c>
       <c r="H98" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="99" spans="1:8">
       <c r="A99" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B99" s="1">
         <v>2</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E99" s="1">
         <v>3</v>
@@ -3854,21 +3849,21 @@
         <v>2</v>
       </c>
       <c r="H99" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="100" spans="1:8">
       <c r="A100" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B100" s="1">
         <v>2</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E100" s="1">
         <v>5</v>
@@ -3880,21 +3875,21 @@
         <v>2</v>
       </c>
       <c r="H100" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="101" spans="1:8">
       <c r="A101" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B101" s="1">
         <v>2</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E101" s="1">
         <v>7</v>
@@ -3906,21 +3901,21 @@
         <v>2</v>
       </c>
       <c r="H101" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="102" spans="1:8">
       <c r="A102" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B102" s="1">
         <v>2</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E102" s="1">
         <v>9</v>
@@ -3932,21 +3927,21 @@
         <v>2</v>
       </c>
       <c r="H102" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="103" spans="1:8">
       <c r="A103" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B103" s="1">
         <v>2</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E103" s="1">
         <v>11</v>
@@ -3958,21 +3953,21 @@
         <v>2</v>
       </c>
       <c r="H103" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="104" spans="1:8">
       <c r="A104" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="B104" s="1">
+        <v>2</v>
+      </c>
+      <c r="C104" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="B104" s="1">
-        <v>2</v>
-      </c>
-      <c r="C104" s="1" t="s">
-        <v>147</v>
-      </c>
       <c r="D104" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E104" s="1">
         <v>13</v>
@@ -3984,21 +3979,21 @@
         <v>2</v>
       </c>
       <c r="H104" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="105" spans="1:8">
       <c r="A105" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B105" s="1">
         <v>2</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E105" s="1">
         <v>15</v>
@@ -4010,21 +4005,21 @@
         <v>2</v>
       </c>
       <c r="H105" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="106" spans="1:8">
       <c r="A106" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B106" s="1">
         <v>2</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E106" s="1">
         <v>17</v>
@@ -4036,21 +4031,21 @@
         <v>2</v>
       </c>
       <c r="H106" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="107" spans="1:8">
       <c r="A107" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B107" s="1">
         <v>6</v>
       </c>
       <c r="C107" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E107" s="1">
         <v>19</v>
@@ -4062,22 +4057,22 @@
         <v>2</v>
       </c>
       <c r="H107" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="108" spans="1:8">
       <c r="A108" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B108" s="1">
         <v>2</v>
       </c>
       <c r="C108" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="D108" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="D108" s="1" t="s">
-        <v>151</v>
-      </c>
       <c r="E108" s="1">
         <v>1</v>
       </c>
@@ -4088,21 +4083,21 @@
         <v>2</v>
       </c>
       <c r="H108" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="109" spans="1:8">
       <c r="A109" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B109" s="1">
         <v>2</v>
       </c>
       <c r="C109" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E109" s="1">
         <v>3</v>
@@ -4114,21 +4109,21 @@
         <v>2</v>
       </c>
       <c r="H109" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="110" spans="1:8">
       <c r="A110" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B110" s="1">
         <v>2</v>
       </c>
       <c r="C110" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E110" s="1">
         <v>5</v>
@@ -4140,21 +4135,21 @@
         <v>2</v>
       </c>
       <c r="H110" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="111" spans="1:8">
       <c r="A111" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B111" s="1">
         <v>2</v>
       </c>
       <c r="C111" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E111" s="1">
         <v>7</v>
@@ -4166,21 +4161,21 @@
         <v>2</v>
       </c>
       <c r="H111" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="112" spans="1:8">
       <c r="A112" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B112" s="1">
         <v>2</v>
       </c>
       <c r="C112" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E112" s="1">
         <v>9</v>
@@ -4192,21 +4187,21 @@
         <v>2</v>
       </c>
       <c r="H112" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="113" spans="1:8">
       <c r="A113" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B113" s="1">
         <v>2</v>
       </c>
       <c r="C113" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E113" s="1">
         <v>11</v>
@@ -4218,21 +4213,21 @@
         <v>2</v>
       </c>
       <c r="H113" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="114" spans="1:8">
       <c r="A114" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B114" s="1">
         <v>8</v>
       </c>
       <c r="C114" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E114" s="1">
         <v>13</v>
@@ -4244,21 +4239,21 @@
         <v>2</v>
       </c>
       <c r="H114" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="115" spans="1:8">
       <c r="A115" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B115" s="1">
         <v>2</v>
       </c>
       <c r="C115" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E115" s="1">
         <v>21</v>
@@ -4270,21 +4265,21 @@
         <v>2</v>
       </c>
       <c r="H115" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="116" spans="1:8">
       <c r="A116" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B116" s="1">
         <v>2</v>
       </c>
       <c r="C116" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E116" s="1">
         <v>23</v>
@@ -4296,22 +4291,22 @@
         <v>2</v>
       </c>
       <c r="H116" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="117" spans="1:8">
       <c r="A117" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B117" s="1">
         <v>1</v>
       </c>
       <c r="C117" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="D117" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="D117" s="1" t="s">
-        <v>158</v>
-      </c>
       <c r="E117" s="1">
         <v>1</v>
       </c>
@@ -4322,21 +4317,21 @@
         <v>1</v>
       </c>
       <c r="H117" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="118" spans="1:8">
       <c r="A118" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B118" s="1">
         <v>1</v>
       </c>
       <c r="C118" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E118" s="1">
         <v>2</v>
@@ -4348,21 +4343,21 @@
         <v>1</v>
       </c>
       <c r="H118" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="119" spans="1:8">
       <c r="A119" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B119" s="1">
         <v>1</v>
       </c>
       <c r="C119" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E119" s="1">
         <v>3</v>
@@ -4374,21 +4369,21 @@
         <v>1</v>
       </c>
       <c r="H119" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="120" spans="1:8">
       <c r="A120" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B120" s="1">
         <v>1</v>
       </c>
       <c r="C120" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E120" s="1">
         <v>4</v>
@@ -4400,21 +4395,21 @@
         <v>1</v>
       </c>
       <c r="H120" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="121" spans="1:8">
       <c r="A121" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B121" s="1">
         <v>1</v>
       </c>
       <c r="C121" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E121" s="1">
         <v>5</v>
@@ -4426,21 +4421,21 @@
         <v>1</v>
       </c>
       <c r="H121" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="122" spans="1:8">
       <c r="A122" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B122" s="1">
         <v>1</v>
       </c>
       <c r="C122" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E122" s="1">
         <v>6</v>
@@ -4452,21 +4447,21 @@
         <v>1</v>
       </c>
       <c r="H122" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="123" spans="1:8">
       <c r="A123" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B123" s="1">
         <v>1</v>
       </c>
       <c r="C123" s="1" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E123" s="1">
         <v>7</v>
@@ -4478,21 +4473,21 @@
         <v>1</v>
       </c>
       <c r="H123" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="124" spans="1:8">
       <c r="A124" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B124" s="1">
         <v>2</v>
       </c>
       <c r="C124" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E124" s="1">
         <v>8</v>
@@ -4504,21 +4499,21 @@
         <v>2</v>
       </c>
       <c r="H124" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="125" spans="1:8">
       <c r="A125" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B125" s="1">
         <v>2</v>
       </c>
       <c r="C125" s="1" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E125" s="1">
         <v>10</v>
@@ -4530,21 +4525,21 @@
         <v>2</v>
       </c>
       <c r="H125" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="126" spans="1:8">
       <c r="A126" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B126" s="1">
         <v>1</v>
       </c>
       <c r="C126" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E126" s="1">
         <v>12</v>
@@ -4556,21 +4551,21 @@
         <v>1</v>
       </c>
       <c r="H126" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="127" spans="1:8">
       <c r="A127" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B127" s="1">
         <v>1</v>
       </c>
       <c r="C127" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E127" s="1">
         <v>13</v>
@@ -4582,21 +4577,21 @@
         <v>1</v>
       </c>
       <c r="H127" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="128" spans="1:8">
       <c r="A128" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B128" s="1">
         <v>1</v>
       </c>
       <c r="C128" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E128" s="1">
         <v>14</v>
@@ -4608,21 +4603,21 @@
         <v>1</v>
       </c>
       <c r="H128" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="129" spans="1:8">
       <c r="A129" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B129" s="1">
         <v>1</v>
       </c>
       <c r="C129" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E129" s="1">
         <v>15</v>
@@ -4634,21 +4629,21 @@
         <v>1</v>
       </c>
       <c r="H129" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="130" spans="1:8">
       <c r="A130" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B130" s="1">
         <v>1</v>
       </c>
       <c r="C130" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E130" s="1">
         <v>16</v>
@@ -4660,21 +4655,21 @@
         <v>1</v>
       </c>
       <c r="H130" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="131" spans="1:8">
       <c r="A131" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B131" s="1">
         <v>1</v>
       </c>
       <c r="C131" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E131" s="1">
         <v>17</v>
@@ -4686,21 +4681,21 @@
         <v>1</v>
       </c>
       <c r="H131" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="132" spans="1:8">
       <c r="A132" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B132" s="1">
         <v>1</v>
       </c>
       <c r="C132" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E132" s="1">
         <v>18</v>
@@ -4712,21 +4707,21 @@
         <v>1</v>
       </c>
       <c r="H132" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="133" spans="1:8">
       <c r="A133" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B133" s="1">
         <v>1</v>
       </c>
       <c r="C133" s="1" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E133" s="1">
         <v>19</v>
@@ -4738,21 +4733,21 @@
         <v>1</v>
       </c>
       <c r="H133" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="134" spans="1:8">
       <c r="A134" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B134" s="1">
         <v>2</v>
       </c>
       <c r="C134" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E134" s="1">
         <v>20</v>
@@ -4764,21 +4759,21 @@
         <v>2</v>
       </c>
       <c r="H134" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="135" spans="1:8">
       <c r="A135" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B135" s="1">
         <v>2</v>
       </c>
       <c r="C135" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="D135" s="1" t="s">
         <v>166</v>
-      </c>
-      <c r="D135" s="1" t="s">
-        <v>167</v>
       </c>
       <c r="E135" s="1">
         <v>22</v>
@@ -4790,21 +4785,21 @@
         <v>2</v>
       </c>
       <c r="H135" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="136" spans="1:8">
       <c r="A136" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B136" s="1">
         <v>1</v>
       </c>
       <c r="C136" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E136" s="1">
         <v>24</v>
@@ -4816,21 +4811,21 @@
         <v>1</v>
       </c>
       <c r="H136" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="137" spans="1:8">
       <c r="A137" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B137" s="1">
         <v>12</v>
       </c>
       <c r="C137" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E137" s="1">
         <v>1</v>
@@ -4842,21 +4837,21 @@
         <v>2</v>
       </c>
       <c r="H137" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="138" spans="1:8">
       <c r="A138" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B138" s="1">
         <v>12</v>
       </c>
       <c r="C138" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E138" s="1">
         <v>13</v>
@@ -4868,22 +4863,22 @@
         <v>2</v>
       </c>
       <c r="H138" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="139" spans="1:8">
       <c r="A139" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="B139" s="1">
+        <v>2</v>
+      </c>
+      <c r="C139" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="B139" s="1">
-        <v>2</v>
-      </c>
-      <c r="C139" s="1" t="s">
+      <c r="D139" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="D139" s="1" t="s">
-        <v>171</v>
-      </c>
       <c r="E139" s="1">
         <v>1</v>
       </c>
@@ -4894,21 +4889,21 @@
         <v>2</v>
       </c>
       <c r="H139" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="140" spans="1:8">
       <c r="A140" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B140" s="1">
         <v>2</v>
       </c>
       <c r="C140" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="E140" s="1">
         <v>3</v>
@@ -4920,21 +4915,21 @@
         <v>2</v>
       </c>
       <c r="H140" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="141" spans="1:8">
       <c r="A141" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B141" s="1">
         <v>2</v>
       </c>
       <c r="C141" s="1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="E141" s="1">
         <v>5</v>
@@ -4946,21 +4941,21 @@
         <v>2</v>
       </c>
       <c r="H141" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="142" spans="1:8">
       <c r="A142" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B142" s="1">
         <v>2</v>
       </c>
       <c r="C142" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="E142" s="1">
         <v>7</v>
@@ -4972,21 +4967,21 @@
         <v>2</v>
       </c>
       <c r="H142" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="143" spans="1:8">
       <c r="A143" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B143" s="1">
         <v>4</v>
       </c>
       <c r="C143" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="E143" s="1">
         <v>9</v>
@@ -4998,21 +4993,21 @@
         <v>2</v>
       </c>
       <c r="H143" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="144" spans="1:8">
       <c r="A144" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B144" s="1">
         <v>2</v>
       </c>
       <c r="C144" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="E144" s="1">
         <v>13</v>
@@ -5024,21 +5019,21 @@
         <v>2</v>
       </c>
       <c r="H144" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="145" spans="1:8">
       <c r="A145" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B145" s="1">
         <v>2</v>
       </c>
       <c r="C145" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="E145" s="1">
         <v>15</v>
@@ -5050,21 +5045,21 @@
         <v>2</v>
       </c>
       <c r="H145" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="146" spans="1:8">
       <c r="A146" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B146" s="1">
         <v>2</v>
       </c>
       <c r="C146" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="E146" s="1">
         <v>17</v>
@@ -5076,21 +5071,21 @@
         <v>2</v>
       </c>
       <c r="H146" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="147" spans="1:8">
       <c r="A147" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B147" s="1">
         <v>2</v>
       </c>
       <c r="C147" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="E147" s="1">
         <v>19</v>
@@ -5102,21 +5097,21 @@
         <v>2</v>
       </c>
       <c r="H147" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="148" spans="1:8">
       <c r="A148" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B148" s="1">
         <v>4</v>
       </c>
       <c r="C148" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="E148" s="1">
         <v>21</v>
@@ -5128,22 +5123,22 @@
         <v>2</v>
       </c>
       <c r="H148" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="149" spans="1:8">
       <c r="A149" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B149" s="1">
         <v>2</v>
       </c>
       <c r="C149" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="D149" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="D149" s="1" t="s">
-        <v>180</v>
-      </c>
       <c r="E149" s="1">
         <v>1</v>
       </c>
@@ -5154,21 +5149,21 @@
         <v>2</v>
       </c>
       <c r="H149" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="150" spans="1:8">
       <c r="A150" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B150" s="1">
         <v>2</v>
       </c>
       <c r="C150" s="1" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E150" s="1">
         <v>3</v>
@@ -5180,21 +5175,21 @@
         <v>2</v>
       </c>
       <c r="H150" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="151" spans="1:8">
       <c r="A151" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B151" s="1">
         <v>2</v>
       </c>
       <c r="C151" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E151" s="1">
         <v>5</v>
@@ -5206,21 +5201,21 @@
         <v>2</v>
       </c>
       <c r="H151" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="152" spans="1:8">
       <c r="A152" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B152" s="1">
         <v>2</v>
       </c>
       <c r="C152" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E152" s="1">
         <v>7</v>
@@ -5232,21 +5227,21 @@
         <v>2</v>
       </c>
       <c r="H152" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="153" spans="1:8">
       <c r="A153" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B153" s="1">
         <v>2</v>
       </c>
       <c r="C153" s="1" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E153" s="1">
         <v>9</v>
@@ -5258,21 +5253,21 @@
         <v>2</v>
       </c>
       <c r="H153" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="154" spans="1:8">
       <c r="A154" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B154" s="1">
         <v>2</v>
       </c>
       <c r="C154" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E154" s="1">
         <v>11</v>
@@ -5284,21 +5279,21 @@
         <v>2</v>
       </c>
       <c r="H154" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="155" spans="1:8">
       <c r="A155" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B155" s="1">
         <v>2</v>
       </c>
       <c r="C155" s="1" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E155" s="1">
         <v>13</v>
@@ -5310,21 +5305,21 @@
         <v>2</v>
       </c>
       <c r="H155" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="156" spans="1:8">
       <c r="A156" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B156" s="1">
         <v>2</v>
       </c>
       <c r="C156" s="1" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E156" s="1">
         <v>15</v>
@@ -5336,21 +5331,21 @@
         <v>2</v>
       </c>
       <c r="H156" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="157" spans="1:8">
       <c r="A157" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B157" s="1">
         <v>2</v>
       </c>
       <c r="C157" s="1" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E157" s="1">
         <v>17</v>
@@ -5362,21 +5357,21 @@
         <v>2</v>
       </c>
       <c r="H157" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="158" spans="1:8">
       <c r="A158" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B158" s="1">
         <v>6</v>
       </c>
       <c r="C158" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E158" s="1">
         <v>19</v>
@@ -5388,21 +5383,21 @@
         <v>2</v>
       </c>
       <c r="H158" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="159" spans="1:8">
       <c r="A159" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B159" s="1">
         <v>12</v>
       </c>
       <c r="C159" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E159" s="1">
         <v>1</v>
@@ -5414,21 +5409,21 @@
         <v>2</v>
       </c>
       <c r="H159" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="160" spans="1:8">
       <c r="A160" s="1" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B160" s="1">
         <v>8</v>
       </c>
       <c r="C160" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E160" s="1">
         <v>13</v>
@@ -5440,21 +5435,21 @@
         <v>2</v>
       </c>
       <c r="H160" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="161" spans="1:8">
       <c r="A161" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="B161" s="1">
+        <v>2</v>
+      </c>
+      <c r="C161" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="B161" s="1">
-        <v>2</v>
-      </c>
-      <c r="C161" s="1" t="s">
-        <v>189</v>
-      </c>
       <c r="D161" s="1" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E161" s="1">
         <v>21</v>
@@ -5466,21 +5461,21 @@
         <v>2</v>
       </c>
       <c r="H161" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="162" spans="1:8">
       <c r="A162" s="1" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B162" s="1">
         <v>2</v>
       </c>
       <c r="C162" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E162" s="1">
         <v>23</v>
@@ -5492,22 +5487,22 @@
         <v>2</v>
       </c>
       <c r="H162" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="163" spans="1:8">
       <c r="A163" s="1" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B163" s="1">
         <v>2</v>
       </c>
       <c r="C163" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="D163" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="D163" s="1" t="s">
-        <v>192</v>
-      </c>
       <c r="E163" s="1">
         <v>1</v>
       </c>
@@ -5518,21 +5513,21 @@
         <v>2</v>
       </c>
       <c r="H163" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="164" spans="1:8">
       <c r="A164" s="1" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B164" s="1">
         <v>2</v>
       </c>
       <c r="C164" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E164" s="1">
         <v>3</v>
@@ -5544,21 +5539,21 @@
         <v>2</v>
       </c>
       <c r="H164" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="165" spans="1:8">
       <c r="A165" s="1" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B165" s="1">
         <v>8</v>
       </c>
       <c r="C165" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E165" s="1">
         <v>5</v>
@@ -5570,22 +5565,22 @@
         <v>2</v>
       </c>
       <c r="H165" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="166" spans="1:8">
       <c r="A166" s="1" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B166" s="1">
         <v>2</v>
       </c>
       <c r="C166" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="D166" s="1" t="s">
         <v>194</v>
       </c>
-      <c r="D166" s="1" t="s">
-        <v>195</v>
-      </c>
       <c r="E166" s="1">
         <v>1</v>
       </c>
@@ -5596,21 +5591,21 @@
         <v>2</v>
       </c>
       <c r="H166" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="167" spans="1:8">
       <c r="A167" s="1" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B167" s="1">
         <v>2</v>
       </c>
       <c r="C167" s="1" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="E167" s="1">
         <v>3</v>
@@ -5622,21 +5617,21 @@
         <v>2</v>
       </c>
       <c r="H167" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="168" spans="1:8">
       <c r="A168" s="1" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B168" s="1">
         <v>8</v>
       </c>
       <c r="C168" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D168" s="1" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="E168" s="1">
         <v>5</v>
@@ -5648,22 +5643,22 @@
         <v>2</v>
       </c>
       <c r="H168" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="169" spans="1:8">
       <c r="A169" s="1" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B169" s="1">
         <v>2</v>
       </c>
       <c r="C169" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="D169" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="D169" s="1" t="s">
-        <v>198</v>
-      </c>
       <c r="E169" s="1">
         <v>1</v>
       </c>
@@ -5674,21 +5669,21 @@
         <v>2</v>
       </c>
       <c r="H169" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="170" spans="1:8">
       <c r="A170" s="1" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B170" s="1">
         <v>2</v>
       </c>
       <c r="C170" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D170" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E170" s="1">
         <v>3</v>
@@ -5700,21 +5695,21 @@
         <v>2</v>
       </c>
       <c r="H170" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="171" spans="1:8">
       <c r="A171" s="1" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B171" s="1">
         <v>8</v>
       </c>
       <c r="C171" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D171" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E171" s="1">
         <v>5</v>
@@ -5726,22 +5721,22 @@
         <v>2</v>
       </c>
       <c r="H171" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="172" spans="1:8">
       <c r="A172" s="1" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B172" s="1">
         <v>2</v>
       </c>
       <c r="C172" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="D172" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="D172" s="1" t="s">
-        <v>201</v>
-      </c>
       <c r="E172" s="1">
         <v>1</v>
       </c>
@@ -5752,21 +5747,21 @@
         <v>2</v>
       </c>
       <c r="H172" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="173" spans="1:8">
       <c r="A173" s="1" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B173" s="1">
         <v>2</v>
       </c>
       <c r="C173" s="1" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D173" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E173" s="1">
         <v>3</v>
@@ -5778,21 +5773,21 @@
         <v>2</v>
       </c>
       <c r="H173" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="174" spans="1:8">
       <c r="A174" s="1" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B174" s="1">
         <v>1</v>
       </c>
       <c r="C174" s="1" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D174" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E174" s="1">
         <v>5</v>
@@ -5804,21 +5799,21 @@
         <v>1</v>
       </c>
       <c r="H174" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="175" spans="1:8">
       <c r="A175" s="1" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B175" s="1">
         <v>1</v>
       </c>
       <c r="C175" s="1" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D175" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E175" s="1">
         <v>6</v>
@@ -5830,21 +5825,21 @@
         <v>1</v>
       </c>
       <c r="H175" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="176" spans="1:8">
       <c r="A176" s="1" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B176" s="1">
         <v>2</v>
       </c>
       <c r="C176" s="1" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D176" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E176" s="1">
         <v>7</v>
@@ -5856,21 +5851,21 @@
         <v>2</v>
       </c>
       <c r="H176" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="177" spans="1:8">
       <c r="A177" s="1" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B177" s="1">
         <v>1</v>
       </c>
       <c r="C177" s="1" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="D177" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E177" s="1">
         <v>9</v>
@@ -5882,21 +5877,21 @@
         <v>1</v>
       </c>
       <c r="H177" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="178" spans="1:8">
       <c r="A178" s="1" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B178" s="1">
         <v>1</v>
       </c>
       <c r="C178" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="D178" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E178" s="1">
         <v>10</v>
@@ -5908,21 +5903,21 @@
         <v>1</v>
       </c>
       <c r="H178" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="179" spans="1:8">
       <c r="A179" s="1" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B179" s="1">
         <v>2</v>
       </c>
       <c r="C179" s="1" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D179" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E179" s="1">
         <v>11</v>
@@ -5934,21 +5929,21 @@
         <v>2</v>
       </c>
       <c r="H179" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="180" spans="1:8">
       <c r="A180" s="1" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B180" s="1">
         <v>2</v>
       </c>
       <c r="C180" s="1" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="D180" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E180" s="1">
         <v>1</v>
@@ -5960,21 +5955,21 @@
         <v>2</v>
       </c>
       <c r="H180" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="181" spans="1:8">
       <c r="A181" s="1" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B181" s="1">
         <v>2</v>
       </c>
       <c r="C181" s="1" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="D181" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E181" s="1">
         <v>3</v>
@@ -5986,21 +5981,21 @@
         <v>2</v>
       </c>
       <c r="H181" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="182" spans="1:8">
       <c r="A182" s="1" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B182" s="1">
         <v>2</v>
       </c>
       <c r="C182" s="1" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D182" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E182" s="1">
         <v>5</v>
@@ -6012,21 +6007,21 @@
         <v>2</v>
       </c>
       <c r="H182" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="183" spans="1:8">
       <c r="A183" s="1" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B183" s="1">
         <v>2</v>
       </c>
       <c r="C183" s="1" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="D183" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E183" s="1">
         <v>7</v>
@@ -6038,21 +6033,21 @@
         <v>2</v>
       </c>
       <c r="H183" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="184" spans="1:8">
       <c r="A184" s="1" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B184" s="1">
         <v>2</v>
       </c>
       <c r="C184" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D184" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E184" s="1">
         <v>9</v>
@@ -6064,21 +6059,21 @@
         <v>2</v>
       </c>
       <c r="H184" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="185" spans="1:8">
       <c r="A185" s="1" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B185" s="1">
         <v>2</v>
       </c>
       <c r="C185" s="1" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="D185" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E185" s="1">
         <v>11</v>
@@ -6090,7 +6085,7 @@
         <v>2</v>
       </c>
       <c r="H185" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="186" spans="1:8">

--- a/CTR_Sample_Template.xlsx
+++ b/CTR_Sample_Template.xlsx
@@ -668,13 +668,13 @@
     <t>date</t>
   </si>
   <si>
-    <t>total_page_no</t>
-  </si>
-  <si>
     <t>sip_no</t>
   </si>
   <si>
     <t>ctr_name</t>
+  </si>
+  <si>
+    <t>total_page</t>
   </si>
 </sst>
 </file>
@@ -1035,7 +1035,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>1</v>
@@ -1056,10 +1056,10 @@
         <v>6</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="K1" s="1" t="s">
         <v>213</v>

--- a/CTR_Sample_Template.xlsx
+++ b/CTR_Sample_Template.xlsx
@@ -4,11 +4,11 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="16380" windowHeight="8190" tabRatio="500"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="16380" windowHeight="8190" tabRatio="500" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="1" r:id="rId1"/>
-    <sheet name="Diagram" sheetId="2" r:id="rId2"/>
+    <sheet name="Fuse Diagram" sheetId="2" r:id="rId2"/>
     <sheet name="RowDetail" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" iterateDelta="1E-4"/>
